--- a/data/employee_data_with_results.xlsx
+++ b/data/employee_data_with_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,17 +532,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,28 +552,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>kavya@company.com</t>
+          <t>arjun@company.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>kavya@gmail.com</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>arjun99@gmail.com</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>45458</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>33977</v>
+      </c>
       <c r="K2" t="n">
-        <v>9234002222</v>
+        <v>9876543210</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -582,7 +586,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1000 0002 0012</t>
+          <t>1000 0002 4001</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -592,7 +596,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>T. Nagar, Chennai</t>
+          <t>Velachery, Chennai</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -601,7 +605,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>68000</v>
+        <v>48000</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -610,19 +614,19 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EMP49942A</t>
+          <t>EMP954BE3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pranav</t>
+          <t>Meera</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -637,51 +641,51 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pranav@company.com</t>
+          <t>meera@company.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>pranav@gmail.com</t>
+          <t>meera88@gmail.com</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45208</v>
+        <v>45495</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37903</v>
+        <v>35934</v>
       </c>
       <c r="K3" t="n">
-        <v>9345003333</v>
+        <v>9123456780</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Welcome@l2</t>
+          <t>Welcome@l1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1000 0002 0013</t>
+          <t>1000 0002 4002</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AB-</t>
+          <t>O+</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Velachery, Chennai</t>
+          <t>Gandhipuram, Coimbatore</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -690,7 +694,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>28000</v>
+        <v>33000</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -699,19 +703,19 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>EMP0BD22A</t>
+          <t>EMP65787C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swathi</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -726,7 +730,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -736,37 +740,41 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>swathi@company.com</t>
+          <t>vikram@company.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>swathi@gmail.com</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>vikram12@gmail.com</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>45026</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>33940</v>
+      </c>
       <c r="K4" t="n">
-        <v>9456004444</v>
+        <v>9090876543</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Welcome@l3</t>
+          <t>Welcome@l1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1000 0002 0014</t>
+          <t>1000 0002 4003</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Saibaba Colony, CBE</t>
+          <t>Tambaram, Chennai</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -775,7 +783,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>36000</v>
+        <v>46000</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -784,511 +792,9 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>EMPE1CA23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Harish</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Project Lead</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9 Years</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>harish@company.com</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>harish@gmail.com</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>9567005555</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Welcome@l4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1000 0002 0015</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Anna Salai, Chennai</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>75000</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>EMPD1D98C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pooja</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>pooja@company.com</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>pooja@gmail.com</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>9678006666</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Welcome@l5</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1000 0002 0016</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>RS Puram, Coimbatore</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>EMPC27233</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>6 Years</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>surya@company.com</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>surya@gmail.com</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>9789007777</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Welcome@l6</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1000 0002 0017</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>AB+</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Chrompet, Chennai</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>52000</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>EMPD4A751</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nisha</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Business Consultant</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5 Years</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nisha@company.com</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>nisha@gmail.com</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>9890008888</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Welcome@l7</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1000 0002 0018</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>O+</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>KK Nagar, Trichy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>48000</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ajay</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Operations Lead</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>8 Years</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ajay@company.com</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ajay@gmail.com</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>9901009999</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Welcome@l8</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1000 0002 0019</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Singanallur, CBE</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>61000</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Shalini</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Content Strategist</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>shalini@company.com</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>shalini@gmail.com</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>45638</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>37967</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9012000000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Welcome@l9</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1000 0002 0020</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Gandhipuram, CBE</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>PF not Applicable</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>30000</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>EMP9BAA18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
